--- a/Valores_Nulos/Actividad 2.2/Análisis_de_Piso.xlsx
+++ b/Valores_Nulos/Actividad 2.2/Análisis_de_Piso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfre\OneDrive\Documentos\Tec de Monterrey\2026 Semestre B_Tercio _1\Plataformas de analítica de negocios para organizaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paty\Desktop\ITESM\8. Quinto Semestre\1. Extracción de Datos\Valores_Nulos\Actividad 2.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1E07822-85FF-48B8-9D60-8199BE7A318F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571D6359-1C65-4B22-B7A8-190F29516896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9D25D404-AABD-460B-B7D6-2201FEA92FC3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{9D25D404-AABD-460B-B7D6-2201FEA92FC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="66">
   <si>
     <t>Leads Piso 2024</t>
   </si>
@@ -65,51 +65,6 @@
     <t xml:space="preserve">* se actualiza al reportar en Sale-U </t>
   </si>
   <si>
-    <t xml:space="preserve">Factor minimo mejor vendedor </t>
-  </si>
-  <si>
-    <t>Leads Prom X Mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T. Ventas Piso </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factor   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de Ventas Historicas </t>
-  </si>
-  <si>
-    <t>RAKING VENTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dependencia de Piso </t>
-  </si>
-  <si>
-    <t>Historico de PDM</t>
-  </si>
-  <si>
-    <t>Historico de SDC</t>
-  </si>
-  <si>
-    <t>Conversion PDM</t>
-  </si>
-  <si>
-    <t>Conversion SDC</t>
-  </si>
-  <si>
-    <t>Factor  PDM</t>
-  </si>
-  <si>
-    <t>Factor  SDC</t>
-  </si>
-  <si>
-    <t>Raking PDM</t>
-  </si>
-  <si>
-    <t>Raking SDC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Asesor </t>
   </si>
   <si>
@@ -161,57 +116,24 @@
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>5.00</t>
-  </si>
-  <si>
     <t>ALAN GONZALES</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>3.28</t>
-  </si>
-  <si>
-    <t>2.22</t>
-  </si>
-  <si>
     <t>ALICIA LEDESMA</t>
   </si>
   <si>
-    <t>0.00</t>
-  </si>
-  <si>
     <t>AURELIO FELIPE</t>
   </si>
   <si>
-    <t>3.50</t>
-  </si>
-  <si>
-    <t>3.88</t>
-  </si>
-  <si>
     <t>CARLOS ALBERTO NIETO</t>
   </si>
   <si>
-    <t>4.27</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARLOS TEXIS </t>
   </si>
   <si>
-    <t>5.25</t>
-  </si>
-  <si>
-    <t>6.50</t>
-  </si>
-  <si>
     <t>CARLOS MANUEL CARMONA</t>
   </si>
   <si>
@@ -221,42 +143,18 @@
     <t xml:space="preserve">CLAUDIA GALVAN </t>
   </si>
   <si>
-    <t>12.50</t>
-  </si>
-  <si>
-    <t>11.00</t>
-  </si>
-  <si>
     <t>CASA</t>
   </si>
   <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>1.52</t>
-  </si>
-  <si>
     <t>DANIEL DE LEON CANDIA</t>
   </si>
   <si>
-    <t>3.00</t>
-  </si>
-  <si>
-    <t>2.08</t>
-  </si>
-  <si>
     <t>DAVID JIMENEZ</t>
   </si>
   <si>
-    <t>19.00</t>
-  </si>
-  <si>
     <t>Demo Vendedor</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>GUADALUPE PEREZ</t>
   </si>
   <si>
@@ -266,24 +164,12 @@
     <t xml:space="preserve">USUARIO DE BDC Y CASA </t>
   </si>
   <si>
-    <t>1.55</t>
-  </si>
-  <si>
     <t>JAIME GONZALEZ</t>
   </si>
   <si>
-    <t>1.36</t>
-  </si>
-  <si>
-    <t>2.44</t>
-  </si>
-  <si>
     <t>JESUS SERRANO</t>
   </si>
   <si>
-    <t>9.00</t>
-  </si>
-  <si>
     <t>JOSE CARLOS  ZENTENO</t>
   </si>
   <si>
@@ -293,21 +179,12 @@
     <t>JOSE MANUEL  LOPEZ</t>
   </si>
   <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>1.67</t>
-  </si>
-  <si>
     <t>JOSE MANUEL LOPEZ</t>
   </si>
   <si>
     <t>JOSETTE RAMON</t>
   </si>
   <si>
-    <t>3.06</t>
-  </si>
-  <si>
     <t xml:space="preserve">LAURA LOPEZ </t>
   </si>
   <si>
@@ -320,75 +197,36 @@
     <t>LUISA LBERTO  GOMEZ</t>
   </si>
   <si>
-    <t>4.50</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARIA GUADALUPE PALACIOS </t>
   </si>
   <si>
-    <t>3.43</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAURICIO ALFREDO </t>
   </si>
   <si>
-    <t>3.63</t>
-  </si>
-  <si>
     <t xml:space="preserve">MIGUEL ANGEL SONDEREGGER </t>
   </si>
   <si>
-    <t>4.18</t>
-  </si>
-  <si>
-    <t>2.36</t>
-  </si>
-  <si>
     <t xml:space="preserve">MONICA GISELA FLORES </t>
   </si>
   <si>
     <t xml:space="preserve">NANCY OLASCOAGA </t>
   </si>
   <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>9.17</t>
-  </si>
-  <si>
     <t>NAYELI MONTES DEOCA</t>
   </si>
   <si>
-    <t>4.00</t>
-  </si>
-  <si>
     <t>OSCAR ALONSO</t>
   </si>
   <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>6.00</t>
-  </si>
-  <si>
     <t>PAUL  ROSAS IRIGOYIN</t>
   </si>
   <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>1.50</t>
-  </si>
-  <si>
     <t>PAUL ROSAS</t>
   </si>
   <si>
     <t xml:space="preserve">PEDRO GONZALES </t>
   </si>
   <si>
-    <t>3.42</t>
-  </si>
-  <si>
     <t>RICARDO SILVA HERAS</t>
   </si>
   <si>
@@ -396,19 +234,13 @@
   </si>
   <si>
     <t>VICTOR MANUEL SANCHEZ ARROYO</t>
-  </si>
-  <si>
-    <t>2.19</t>
-  </si>
-  <si>
-    <t>2.71</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,26 +279,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,12 +313,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -506,12 +320,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -527,14 +335,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -626,19 +428,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -735,19 +524,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -769,19 +545,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -790,57 +561,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -860,9 +606,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -900,7 +646,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1006,7 +752,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1148,7 +894,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1156,367 +902,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302D10F2-825A-4D0F-93E4-C7FC3D5E0EC5}">
-  <dimension ref="A1:AY43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:51" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="9" t="s">
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="11" t="s">
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="12"/>
-      <c r="AM1" s="12"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1">
-        <v>263</v>
-      </c>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="13">
-        <v>979</v>
-      </c>
-      <c r="AS1" s="13">
-        <v>811</v>
-      </c>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="12" t="s">
+    </row>
+    <row r="2" spans="1:37" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:37" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-    </row>
-    <row r="2" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="14">
-        <v>459</v>
-      </c>
-      <c r="C2" s="15">
-        <v>27</v>
-      </c>
-      <c r="D2" s="15">
-        <v>95</v>
-      </c>
-      <c r="E2" s="15">
-        <v>110</v>
-      </c>
-      <c r="F2" s="15">
-        <v>65</v>
-      </c>
-      <c r="G2" s="15">
-        <v>107</v>
-      </c>
-      <c r="H2" s="15">
-        <v>88</v>
-      </c>
-      <c r="I2" s="15">
-        <v>59</v>
-      </c>
-      <c r="J2" s="15">
-        <v>40</v>
-      </c>
-      <c r="K2" s="15">
-        <v>53</v>
-      </c>
-      <c r="L2" s="15">
-        <v>67</v>
-      </c>
-      <c r="M2" s="15">
-        <v>71</v>
-      </c>
-      <c r="N2" s="15">
-        <v>61</v>
-      </c>
-      <c r="O2" s="15">
-        <v>80</v>
-      </c>
-      <c r="P2" s="16">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="16">
-        <v>1417</v>
-      </c>
-      <c r="R2" s="16">
-        <v>661</v>
-      </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="17">
-        <v>9</v>
-      </c>
-      <c r="V2" s="18">
-        <v>5</v>
-      </c>
-      <c r="W2" s="18">
-        <v>9</v>
-      </c>
-      <c r="X2" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="18">
-        <v>3</v>
-      </c>
-      <c r="Z2" s="18">
+      <c r="B3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="18">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="18">
-        <v>6</v>
-      </c>
-      <c r="AC2" s="18">
-        <v>3</v>
-      </c>
-      <c r="AD2" s="18">
+      <c r="C3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="AE2" s="18">
-        <v>8</v>
-      </c>
-      <c r="AF2" s="18">
+      <c r="D3" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="AG2" s="18">
+      <c r="O3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="AH2" s="18">
-        <v>9</v>
-      </c>
-      <c r="AI2" s="13">
-        <v>4</v>
-      </c>
-      <c r="AJ2" s="19">
-        <f>SUM(AJ4:AJ43)</f>
-        <v>12</v>
-      </c>
-      <c r="AK2" s="20">
-        <f>SUM(AK4:AK43)</f>
-        <v>3</v>
-      </c>
-      <c r="AL2" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="AN2" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO2" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AP2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ2" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR2" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS2" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AT2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="AU2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV2" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW2" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="AY2" s="26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>37</v>
+      <c r="Q3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="28" t="s">
+      <c r="U3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="W3" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="X3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG3" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK3" s="23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB3" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC3" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD3" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE3" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF3" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG3" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH3" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI3" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ3" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK3" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL3" s="21"/>
-      <c r="AM3" s="21"/>
-      <c r="AN3" s="22"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="34"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>23</v>
@@ -1547,8 +1107,8 @@
       <c r="T4" s="1">
         <v>28</v>
       </c>
-      <c r="U4" s="35" t="s">
-        <v>37</v>
+      <c r="U4" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -1564,56 +1124,14 @@
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="1">
-        <v>23</v>
-      </c>
-      <c r="AQ4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT4" s="37">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AW4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AY4" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK4" s="25"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -1625,7 +1143,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1">
@@ -1655,11 +1173,11 @@
       <c r="S5" s="1">
         <v>8</v>
       </c>
-      <c r="T5" s="39">
+      <c r="T5" s="26">
         <v>3</v>
       </c>
-      <c r="U5" s="35" t="s">
-        <v>37</v>
+      <c r="U5" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
@@ -1690,53 +1208,11 @@
       <c r="AJ5" s="1">
         <v>1</v>
       </c>
-      <c r="AK5" s="36"/>
-      <c r="AL5" s="1">
-        <v>10</v>
-      </c>
-      <c r="AM5" s="1">
-        <v>11</v>
-      </c>
-      <c r="AN5" s="37">
-        <v>0.18</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>18</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>6</v>
-      </c>
-      <c r="AQ5" s="37">
-        <v>0.61</v>
-      </c>
-      <c r="AR5" s="1">
-        <v>59</v>
-      </c>
-      <c r="AS5" s="1">
-        <v>40</v>
-      </c>
-      <c r="AT5" s="37">
-        <v>0.31</v>
-      </c>
-      <c r="AU5" s="38">
-        <v>0.02</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AW5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AX5" s="1">
-        <v>7</v>
-      </c>
-      <c r="AY5" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK5" s="25"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1767,8 +1243,8 @@
       <c r="T6" s="1">
         <v>28</v>
       </c>
-      <c r="U6" s="35" t="s">
-        <v>37</v>
+      <c r="U6" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -1784,50 +1260,14 @@
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="36"/>
-      <c r="AL6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="1"/>
-      <c r="AP6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AS6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AT6" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX6" s="1"/>
-      <c r="AY6" s="1"/>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK6" s="25"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1864,8 +1304,8 @@
       <c r="T7" s="1">
         <v>8</v>
       </c>
-      <c r="U7" s="35" t="s">
-        <v>37</v>
+      <c r="U7" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1885,60 +1325,18 @@
         <v>1</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ7" s="1">
         <v>3</v>
       </c>
-      <c r="AK7" s="36">
-        <v>2</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>8</v>
-      </c>
-      <c r="AM7" s="1">
-        <v>3</v>
-      </c>
-      <c r="AN7" s="37">
-        <v>0.09</v>
-      </c>
-      <c r="AO7" s="1">
-        <v>8</v>
-      </c>
-      <c r="AP7" s="1">
-        <v>11</v>
-      </c>
-      <c r="AQ7" s="37">
-        <v>0.38</v>
-      </c>
-      <c r="AR7" s="1">
-        <v>28</v>
-      </c>
-      <c r="AS7" s="1">
-        <v>31</v>
-      </c>
-      <c r="AT7" s="37">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AU7" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AW7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AX7" s="1">
-        <v>9</v>
-      </c>
-      <c r="AY7" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK7" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1980,11 +1378,11 @@
       <c r="S8" s="1">
         <v>9</v>
       </c>
-      <c r="T8" s="40">
+      <c r="T8" s="27">
         <v>5</v>
       </c>
-      <c r="U8" s="35" t="s">
-        <v>37</v>
+      <c r="U8" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -2008,56 +1406,14 @@
       </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ8" s="1"/>
-      <c r="AK8" s="36"/>
-      <c r="AL8" s="1">
-        <v>7</v>
-      </c>
-      <c r="AM8" s="1">
-        <v>9</v>
-      </c>
-      <c r="AN8" s="37">
-        <v>0.16</v>
-      </c>
-      <c r="AO8" s="1">
-        <v>15</v>
-      </c>
-      <c r="AP8" s="1">
-        <v>8</v>
-      </c>
-      <c r="AQ8" s="37">
-        <v>0.6</v>
-      </c>
-      <c r="AR8" s="1">
-        <v>64</v>
-      </c>
-      <c r="AS8" s="1">
-        <v>30</v>
-      </c>
-      <c r="AT8" s="37">
-        <v>0.23</v>
-      </c>
-      <c r="AU8" s="38">
-        <v>0.02</v>
-      </c>
-      <c r="AV8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX8" s="1">
-        <v>13</v>
-      </c>
-      <c r="AY8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK8" s="25"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2094,8 +1450,8 @@
       <c r="T9" s="1">
         <v>17</v>
       </c>
-      <c r="U9" s="35" t="s">
-        <v>37</v>
+      <c r="U9" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -2113,56 +1469,14 @@
       </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="AO9" s="1">
-        <v>4</v>
-      </c>
-      <c r="AP9" s="1">
-        <v>17</v>
-      </c>
-      <c r="AQ9" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="AR9" s="1">
-        <v>21</v>
-      </c>
-      <c r="AS9" s="1">
-        <v>26</v>
-      </c>
-      <c r="AT9" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="AU9" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AW9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AX9" s="1">
-        <v>18</v>
-      </c>
-      <c r="AY9" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK9" s="25"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>18</v>
@@ -2197,14 +1511,14 @@
       <c r="R10" s="1">
         <v>3</v>
       </c>
-      <c r="S10" s="40">
+      <c r="S10" s="27">
         <v>5</v>
       </c>
       <c r="T10" s="1">
         <v>21</v>
       </c>
-      <c r="U10" s="35" t="s">
-        <v>37</v>
+      <c r="U10" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V10" s="1">
         <v>3</v>
@@ -2226,50 +1540,14 @@
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ10" s="1"/>
-      <c r="AK10" s="36"/>
-      <c r="AL10" s="1">
-        <v>16</v>
-      </c>
-      <c r="AM10" s="1">
-        <v>6</v>
-      </c>
-      <c r="AN10" s="37">
-        <v>0.06</v>
-      </c>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="1">
-        <v>54</v>
-      </c>
-      <c r="AS10" s="1">
-        <v>8</v>
-      </c>
-      <c r="AT10" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX10" s="1"/>
-      <c r="AY10" s="1"/>
-    </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK10" s="25"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2300,8 +1578,8 @@
       <c r="T11" s="1">
         <v>28</v>
       </c>
-      <c r="U11" s="35" t="s">
-        <v>37</v>
+      <c r="U11" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
@@ -2317,50 +1595,14 @@
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS11" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT11" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX11" s="1"/>
-      <c r="AY11" s="1"/>
-    </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK11" s="25"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2393,8 +1635,8 @@
       <c r="T12" s="1">
         <v>21</v>
       </c>
-      <c r="U12" s="35" t="s">
-        <v>37</v>
+      <c r="U12" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -2410,56 +1652,14 @@
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ12" s="1"/>
-      <c r="AK12" s="36"/>
-      <c r="AL12" s="1">
-        <v>2</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="1">
-        <v>2</v>
-      </c>
-      <c r="AP12" s="1">
-        <v>19</v>
-      </c>
-      <c r="AQ12" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="1">
-        <v>25</v>
-      </c>
-      <c r="AS12" s="1">
-        <v>22</v>
-      </c>
-      <c r="AT12" s="37">
-        <v>0.08</v>
-      </c>
-      <c r="AU12" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AW12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX12" s="1">
-        <v>22</v>
-      </c>
-      <c r="AY12" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK12" s="25"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -2502,8 +1702,8 @@
       <c r="T13" s="1">
         <v>17</v>
       </c>
-      <c r="U13" s="35" t="s">
-        <v>37</v>
+      <c r="U13" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
@@ -2523,54 +1723,14 @@
       </c>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ13" s="1"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="1">
-        <v>2</v>
-      </c>
-      <c r="AM13" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN13" s="37">
-        <v>0.15</v>
-      </c>
-      <c r="AO13" s="41">
-        <v>21</v>
-      </c>
-      <c r="AP13" s="1">
-        <v>4</v>
-      </c>
-      <c r="AQ13" s="37">
-        <v>0.1</v>
-      </c>
-      <c r="AR13" s="1">
-        <v>20</v>
-      </c>
-      <c r="AS13" s="1">
-        <v>32</v>
-      </c>
-      <c r="AT13" s="37">
-        <v>1.05</v>
-      </c>
-      <c r="AU13" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX13" s="1"/>
-      <c r="AY13" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK13" s="25"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -2615,8 +1775,8 @@
       <c r="T14" s="1">
         <v>6</v>
       </c>
-      <c r="U14" s="35" t="s">
-        <v>37</v>
+      <c r="U14" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
@@ -2640,56 +1800,14 @@
       </c>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="25"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="AJ14" s="1"/>
-      <c r="AK14" s="36"/>
-      <c r="AL14" s="1">
-        <v>8</v>
-      </c>
-      <c r="AM14" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN14" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AO14" s="1">
-        <v>12</v>
-      </c>
-      <c r="AP14" s="1">
-        <v>9</v>
-      </c>
-      <c r="AQ14" s="37">
-        <v>0.42</v>
-      </c>
-      <c r="AR14" s="1">
-        <v>36</v>
-      </c>
-      <c r="AS14" s="1">
-        <v>25</v>
-      </c>
-      <c r="AT14" s="37">
-        <v>0.33</v>
-      </c>
-      <c r="AU14" s="38">
-        <v>0.02</v>
-      </c>
-      <c r="AV14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX14" s="1">
-        <v>6</v>
-      </c>
-      <c r="AY14" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2724,8 +1842,8 @@
       <c r="T15" s="1">
         <v>28</v>
       </c>
-      <c r="U15" s="35" t="s">
-        <v>37</v>
+      <c r="U15" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
@@ -2741,56 +1859,14 @@
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ15" s="1"/>
-      <c r="AK15" s="36"/>
-      <c r="AL15" s="1">
-        <v>6</v>
-      </c>
-      <c r="AM15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP15" s="1">
-        <v>23</v>
-      </c>
-      <c r="AQ15" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="1">
-        <v>19</v>
-      </c>
-      <c r="AS15" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT15" s="37">
-        <v>0.05</v>
-      </c>
-      <c r="AU15" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX15" s="1">
-        <v>23</v>
-      </c>
-      <c r="AY15" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK15" s="25"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -2827,7 +1903,7 @@
       <c r="T16" s="1">
         <v>21</v>
       </c>
-      <c r="U16" s="35">
+      <c r="U16" s="24">
         <v>2</v>
       </c>
       <c r="V16" s="1">
@@ -2848,50 +1924,14 @@
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ16" s="1"/>
-      <c r="AK16" s="36"/>
-      <c r="AL16" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN16" s="37">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ16" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="1">
-        <v>7</v>
-      </c>
-      <c r="AS16" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT16" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX16" s="1"/>
-      <c r="AY16" s="1"/>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK16" s="25"/>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2926,8 +1966,8 @@
       <c r="T17" s="1">
         <v>28</v>
       </c>
-      <c r="U17" s="35" t="s">
-        <v>37</v>
+      <c r="U17" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -2943,50 +1983,14 @@
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ17" s="1"/>
-      <c r="AK17" s="36"/>
-      <c r="AL17" s="1">
-        <v>4</v>
-      </c>
-      <c r="AM17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="1"/>
-      <c r="AP17" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ17" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="1">
-        <v>8</v>
-      </c>
-      <c r="AS17" s="1">
-        <v>7</v>
-      </c>
-      <c r="AT17" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX17" s="1"/>
-      <c r="AY17" s="1"/>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK17" s="25"/>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
@@ -3025,8 +2029,8 @@
       <c r="T18" s="1">
         <v>17</v>
       </c>
-      <c r="U18" s="35" t="s">
-        <v>37</v>
+      <c r="U18" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -3042,56 +2046,14 @@
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ18" s="1"/>
-      <c r="AK18" s="36"/>
-      <c r="AL18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="1">
-        <v>2</v>
-      </c>
-      <c r="AP18" s="1">
-        <v>19</v>
-      </c>
-      <c r="AQ18" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="1">
-        <v>25</v>
-      </c>
-      <c r="AS18" s="1">
-        <v>22</v>
-      </c>
-      <c r="AT18" s="37">
-        <v>0.08</v>
-      </c>
-      <c r="AU18" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AW18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX18" s="1">
-        <v>22</v>
-      </c>
-      <c r="AY18" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK18" s="25"/>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -3134,8 +2096,8 @@
       <c r="T19" s="1">
         <v>15</v>
       </c>
-      <c r="U19" s="35" t="s">
-        <v>37</v>
+      <c r="U19" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -3151,56 +2113,14 @@
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ19" s="1"/>
-      <c r="AK19" s="36"/>
-      <c r="AL19" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="41">
-        <v>11</v>
-      </c>
-      <c r="AP19" s="1">
-        <v>10</v>
-      </c>
-      <c r="AQ19" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="1">
-        <v>17</v>
-      </c>
-      <c r="AS19" s="1">
-        <v>11</v>
-      </c>
-      <c r="AT19" s="37">
-        <v>0.65</v>
-      </c>
-      <c r="AU19" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AW19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX19" s="1">
-        <v>3</v>
-      </c>
-      <c r="AY19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK19" s="25"/>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -3242,11 +2162,11 @@
       <c r="S20" s="1">
         <v>7</v>
       </c>
-      <c r="T20" s="39">
+      <c r="T20" s="26">
         <v>4</v>
       </c>
-      <c r="U20" s="35" t="s">
-        <v>37</v>
+      <c r="U20" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V20" s="1"/>
       <c r="W20" s="1">
@@ -3272,56 +2192,14 @@
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ20" s="1"/>
-      <c r="AK20" s="36"/>
-      <c r="AL20" s="1">
-        <v>9</v>
-      </c>
-      <c r="AM20" s="1">
-        <v>7</v>
-      </c>
-      <c r="AN20" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AO20" s="1">
-        <v>25</v>
-      </c>
-      <c r="AP20" s="1">
-        <v>3</v>
-      </c>
-      <c r="AQ20" s="37">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AR20" s="1">
-        <v>34</v>
-      </c>
-      <c r="AS20" s="1">
-        <v>61</v>
-      </c>
-      <c r="AT20" s="37">
-        <v>0.74</v>
-      </c>
-      <c r="AU20" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX20" s="1">
-        <v>2</v>
-      </c>
-      <c r="AY20" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK20" s="25"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>114</v>
@@ -3346,13 +2224,13 @@
       <c r="R21" s="1">
         <v>0</v>
       </c>
-      <c r="S21" s="43">
+      <c r="S21" s="2">
         <v>3</v>
       </c>
       <c r="T21" s="1">
         <v>28</v>
       </c>
-      <c r="U21" s="35">
+      <c r="U21" s="24">
         <v>2</v>
       </c>
       <c r="V21" s="1"/>
@@ -3369,56 +2247,14 @@
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ21" s="1"/>
-      <c r="AK21" s="36"/>
-      <c r="AL21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN21" s="37">
-        <v>0.02</v>
-      </c>
-      <c r="AO21" s="1">
-        <v>2</v>
-      </c>
-      <c r="AP21" s="1">
-        <v>19</v>
-      </c>
-      <c r="AQ21" s="37">
-        <v>1</v>
-      </c>
-      <c r="AR21" s="1">
-        <v>18</v>
-      </c>
-      <c r="AS21" s="1">
-        <v>6</v>
-      </c>
-      <c r="AT21" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AU21" s="38">
-        <v>0.17</v>
-      </c>
-      <c r="AV21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AW21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX21" s="1">
-        <v>20</v>
-      </c>
-      <c r="AY21" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK21" s="25"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3449,8 +2285,8 @@
       <c r="T22" s="1">
         <v>16</v>
       </c>
-      <c r="U22" s="35" t="s">
-        <v>37</v>
+      <c r="U22" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -3468,56 +2304,14 @@
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ22" s="1"/>
-      <c r="AK22" s="36"/>
-      <c r="AL22" s="1">
-        <v>8</v>
-      </c>
-      <c r="AM22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN22" s="37">
-        <v>0.13</v>
-      </c>
-      <c r="AO22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP22" s="1">
-        <v>23</v>
-      </c>
-      <c r="AQ22" s="37">
-        <v>1</v>
-      </c>
-      <c r="AR22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AS22" s="1">
-        <v>2</v>
-      </c>
-      <c r="AT22" s="37">
-        <v>0.2</v>
-      </c>
-      <c r="AU22" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="AV22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AW22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX22" s="1">
-        <v>17</v>
-      </c>
-      <c r="AY22" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK22" s="25"/>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -3548,8 +2342,8 @@
       <c r="T23" s="1">
         <v>25</v>
       </c>
-      <c r="U23" s="35" t="s">
-        <v>37</v>
+      <c r="U23" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -3565,50 +2359,14 @@
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ23" s="1"/>
-      <c r="AK23" s="36"/>
-      <c r="AL23" s="1">
-        <v>2</v>
-      </c>
-      <c r="AM23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="1"/>
-      <c r="AP23" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ23" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS23" s="1">
-        <v>8</v>
-      </c>
-      <c r="AT23" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU23" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX23" s="1"/>
-      <c r="AY23" s="1"/>
-    </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK23" s="25"/>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
@@ -3639,7 +2397,7 @@
       <c r="T24" s="1">
         <v>28</v>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="24">
         <v>2</v>
       </c>
       <c r="V24" s="1"/>
@@ -3656,54 +2414,14 @@
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ24" s="1"/>
-      <c r="AK24" s="36"/>
-      <c r="AL24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN24" s="37">
-        <v>1</v>
-      </c>
-      <c r="AO24" s="1">
-        <v>3</v>
-      </c>
-      <c r="AP24" s="1">
-        <v>18</v>
-      </c>
-      <c r="AQ24" s="37">
-        <v>0.67</v>
-      </c>
-      <c r="AR24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AS24" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT24" s="37">
-        <v>3</v>
-      </c>
-      <c r="AU24" s="38">
-        <v>0.13</v>
-      </c>
-      <c r="AV24" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AX24" s="1"/>
-      <c r="AY24" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK24" s="25"/>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1">
         <v>67</v>
@@ -3736,8 +2454,8 @@
       <c r="T25" s="1">
         <v>28</v>
       </c>
-      <c r="U25" s="35" t="s">
-        <v>37</v>
+      <c r="U25" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -3753,51 +2471,14 @@
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ25" s="1"/>
-      <c r="AK25" s="36"/>
-      <c r="AL25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="1"/>
-      <c r="AP25" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ25" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS25" s="1">
-        <v>7</v>
-      </c>
-      <c r="AT25" s="1" t="e">
-        <f>AS25/AR25</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AU25" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV25" s="1" t="s">
+      <c r="AK25" s="25"/>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="AW25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX25" s="1"/>
-      <c r="AY25" s="1"/>
-    </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3840,8 +2521,8 @@
       <c r="T26" s="1">
         <v>7</v>
       </c>
-      <c r="U26" s="35" t="s">
-        <v>37</v>
+      <c r="U26" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -3863,56 +2544,14 @@
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ26" s="1"/>
-      <c r="AK26" s="36"/>
-      <c r="AL26" s="1">
-        <v>7</v>
-      </c>
-      <c r="AM26" s="1">
-        <v>6</v>
-      </c>
-      <c r="AN26" s="37">
-        <v>0.12</v>
-      </c>
-      <c r="AO26" s="1">
-        <v>16</v>
-      </c>
-      <c r="AP26" s="1">
-        <v>7</v>
-      </c>
-      <c r="AQ26" s="37">
-        <v>0.38</v>
-      </c>
-      <c r="AR26" s="1">
-        <v>48</v>
-      </c>
-      <c r="AS26" s="1">
+      <c r="AK26" s="25"/>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="AT26" s="37">
-        <v>0.33</v>
-      </c>
-      <c r="AU26" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX26" s="1">
-        <v>6</v>
-      </c>
-      <c r="AY26" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -3947,8 +2586,8 @@
       <c r="T27" s="1">
         <v>17</v>
       </c>
-      <c r="U27" s="35" t="s">
-        <v>37</v>
+      <c r="U27" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -3964,50 +2603,14 @@
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ27" s="1"/>
-      <c r="AK27" s="36"/>
-      <c r="AL27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="1"/>
-      <c r="AP27" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ27" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS27" s="1">
-        <v>2</v>
-      </c>
-      <c r="AT27" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU27" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX27" s="1"/>
-      <c r="AY27" s="1"/>
-    </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK27" s="25"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
@@ -4042,8 +2645,8 @@
       <c r="T28" s="1">
         <v>28</v>
       </c>
-      <c r="U28" s="35" t="s">
-        <v>37</v>
+      <c r="U28" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -4059,50 +2662,14 @@
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ28" s="1"/>
-      <c r="AK28" s="36"/>
-      <c r="AL28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="1"/>
-      <c r="AP28" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ28" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS28" s="1">
-        <v>3</v>
-      </c>
-      <c r="AT28" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX28" s="1"/>
-      <c r="AY28" s="1"/>
-    </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK28" s="25"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1">
         <v>6</v>
@@ -4137,8 +2704,8 @@
       <c r="T29" s="1">
         <v>25</v>
       </c>
-      <c r="U29" s="35" t="s">
-        <v>37</v>
+      <c r="U29" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -4154,50 +2721,14 @@
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ29" s="1"/>
-      <c r="AK29" s="36"/>
-      <c r="AL29" s="1">
-        <v>2</v>
-      </c>
-      <c r="AM29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="1"/>
-      <c r="AP29" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ29" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR29" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS29" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT29" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX29" s="1"/>
-      <c r="AY29" s="1"/>
-    </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK29" s="25"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B30" s="1">
         <v>42</v>
@@ -4232,7 +2763,7 @@
       <c r="T30" s="1">
         <v>28</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="24">
         <v>1</v>
       </c>
       <c r="V30" s="1"/>
@@ -4249,56 +2780,14 @@
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ30" s="1"/>
-      <c r="AK30" s="36"/>
-      <c r="AL30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="37">
-        <v>0.02</v>
-      </c>
-      <c r="AO30" s="1">
-        <v>2</v>
-      </c>
-      <c r="AP30" s="1">
-        <v>19</v>
-      </c>
-      <c r="AQ30" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="AR30" s="1">
-        <v>9</v>
-      </c>
-      <c r="AS30" s="1">
-        <v>4</v>
-      </c>
-      <c r="AT30" s="37">
-        <v>0.22</v>
-      </c>
-      <c r="AU30" s="38">
-        <v>0.13</v>
-      </c>
-      <c r="AV30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX30" s="1">
-        <v>14</v>
-      </c>
-      <c r="AY30" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK30" s="25"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4333,8 +2822,8 @@
       <c r="T31" s="1">
         <v>9</v>
       </c>
-      <c r="U31" s="35" t="s">
-        <v>37</v>
+      <c r="U31" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -4354,56 +2843,14 @@
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ31" s="1"/>
-      <c r="AK31" s="36"/>
-      <c r="AL31" s="1">
-        <v>9</v>
-      </c>
-      <c r="AM31" s="1">
-        <v>3</v>
-      </c>
-      <c r="AN31" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AO31" s="1">
-        <v>7</v>
-      </c>
-      <c r="AP31" s="1">
-        <v>13</v>
-      </c>
-      <c r="AQ31" s="37">
-        <v>0.43</v>
-      </c>
-      <c r="AR31" s="1">
-        <v>35</v>
-      </c>
-      <c r="AS31" s="1">
-        <v>24</v>
-      </c>
-      <c r="AT31" s="37">
-        <v>0.2</v>
-      </c>
-      <c r="AU31" s="38">
-        <v>0.02</v>
-      </c>
-      <c r="AV31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AW31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX31" s="1">
-        <v>17</v>
-      </c>
-      <c r="AY31" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK31" s="25"/>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4440,8 +2887,8 @@
       <c r="T32" s="1">
         <v>10</v>
       </c>
-      <c r="U32" s="35" t="s">
-        <v>37</v>
+      <c r="U32" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -4466,55 +2913,13 @@
       <c r="AJ32" s="1">
         <v>2</v>
       </c>
-      <c r="AK32" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="1">
-        <v>6</v>
-      </c>
-      <c r="AM32" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN32" s="37">
-        <v>0.18</v>
-      </c>
-      <c r="AO32" s="1">
-        <v>8</v>
-      </c>
-      <c r="AP32" s="1">
-        <v>11</v>
-      </c>
-      <c r="AQ32" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="AR32" s="1">
-        <v>29</v>
-      </c>
-      <c r="AS32" s="1">
-        <v>42</v>
-      </c>
-      <c r="AT32" s="37">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AU32" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AX32" s="1">
-        <v>10</v>
-      </c>
-      <c r="AY32" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK32" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1">
         <v>37</v>
@@ -4561,13 +2966,13 @@
       <c r="R33" s="1">
         <v>108</v>
       </c>
-      <c r="S33" s="44">
-        <v>1</v>
-      </c>
-      <c r="T33" s="44">
-        <v>1</v>
-      </c>
-      <c r="U33" s="35">
+      <c r="S33" s="28">
+        <v>1</v>
+      </c>
+      <c r="T33" s="28">
+        <v>1</v>
+      </c>
+      <c r="U33" s="24">
         <v>1</v>
       </c>
       <c r="V33" s="1"/>
@@ -4598,56 +3003,14 @@
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ33" s="1"/>
-      <c r="AK33" s="36"/>
-      <c r="AL33" s="1">
-        <v>17</v>
-      </c>
-      <c r="AM33" s="1">
-        <v>18</v>
-      </c>
-      <c r="AN33" s="37">
-        <v>0.09</v>
-      </c>
-      <c r="AO33" s="1">
-        <v>28</v>
-      </c>
-      <c r="AP33" s="45">
-        <v>2</v>
-      </c>
-      <c r="AQ33" s="37">
-        <v>0.64</v>
-      </c>
-      <c r="AR33" s="1">
-        <v>117</v>
-      </c>
-      <c r="AS33" s="1">
-        <v>66</v>
-      </c>
-      <c r="AT33" s="37">
-        <v>0.24</v>
-      </c>
-      <c r="AU33" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX33" s="1">
-        <v>12</v>
-      </c>
-      <c r="AY33" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK33" s="25"/>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4684,8 +3047,8 @@
       <c r="T34" s="1">
         <v>13</v>
       </c>
-      <c r="U34" s="35" t="s">
-        <v>37</v>
+      <c r="U34" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -4703,50 +3066,14 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ34" s="1"/>
-      <c r="AK34" s="36"/>
-      <c r="AL34" s="1">
-        <v>4</v>
-      </c>
-      <c r="AM34" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="37">
-        <v>0.06</v>
-      </c>
-      <c r="AO34" s="1"/>
-      <c r="AP34" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ34" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="1">
-        <v>22</v>
-      </c>
-      <c r="AS34" s="1">
-        <v>9</v>
-      </c>
-      <c r="AT34" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX34" s="1"/>
-      <c r="AY34" s="1"/>
-    </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK34" s="25"/>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
@@ -4787,8 +3114,8 @@
       <c r="T35" s="1">
         <v>11</v>
       </c>
-      <c r="U35" s="35" t="s">
-        <v>37</v>
+      <c r="U35" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -4804,56 +3131,14 @@
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ35" s="1"/>
-      <c r="AK35" s="36"/>
-      <c r="AL35" s="1">
-        <v>4</v>
-      </c>
-      <c r="AM35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="1">
-        <v>6</v>
-      </c>
-      <c r="AP35" s="1">
-        <v>14</v>
-      </c>
-      <c r="AQ35" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR35" s="1">
-        <v>48</v>
-      </c>
-      <c r="AS35" s="1">
-        <v>55</v>
-      </c>
-      <c r="AT35" s="37">
-        <v>0.13</v>
-      </c>
-      <c r="AU35" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AW35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX35" s="1">
-        <v>19</v>
-      </c>
-      <c r="AY35" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK35" s="25"/>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="B36" s="1">
         <v>41</v>
@@ -4886,8 +3171,8 @@
       <c r="T36" s="1">
         <v>28</v>
       </c>
-      <c r="U36" s="35" t="s">
-        <v>37</v>
+      <c r="U36" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -4903,56 +3188,14 @@
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ36" s="1"/>
-      <c r="AK36" s="36"/>
-      <c r="AL36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="1">
-        <v>23</v>
-      </c>
-      <c r="AQ36" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR36" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS36" s="1">
-        <v>3</v>
-      </c>
-      <c r="AT36" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="AU36" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV36" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX36" s="1">
-        <v>11</v>
-      </c>
-      <c r="AY36" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK36" s="25"/>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -4991,8 +3234,8 @@
       <c r="T37" s="1">
         <v>14</v>
       </c>
-      <c r="U37" s="35" t="s">
-        <v>37</v>
+      <c r="U37" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -5008,56 +3251,14 @@
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ37" s="1"/>
-      <c r="AK37" s="36"/>
-      <c r="AL37" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="1">
-        <v>6</v>
-      </c>
-      <c r="AP37" s="1">
-        <v>14</v>
-      </c>
-      <c r="AQ37" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="1">
-        <v>29</v>
-      </c>
-      <c r="AS37" s="1">
-        <v>36</v>
-      </c>
-      <c r="AT37" s="37">
-        <v>0.21</v>
-      </c>
-      <c r="AU37" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AW37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX37" s="1">
-        <v>15</v>
-      </c>
-      <c r="AY37" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK37" s="25"/>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
@@ -5090,7 +3291,7 @@
       <c r="T38" s="1">
         <v>28</v>
       </c>
-      <c r="U38" s="35">
+      <c r="U38" s="24">
         <v>1</v>
       </c>
       <c r="V38" s="1"/>
@@ -5109,54 +3310,14 @@
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ38" s="1"/>
-      <c r="AK38" s="36"/>
-      <c r="AL38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="1">
-        <v>5</v>
-      </c>
-      <c r="AN38" s="37">
-        <v>1</v>
-      </c>
-      <c r="AO38" s="1">
-        <v>6</v>
-      </c>
-      <c r="AP38" s="1">
-        <v>14</v>
-      </c>
-      <c r="AQ38" s="37">
-        <v>0.83</v>
-      </c>
-      <c r="AR38" s="1">
-        <v>5</v>
-      </c>
-      <c r="AS38" s="1">
-        <v>9</v>
-      </c>
-      <c r="AT38" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="AU38" s="38">
-        <v>0.09</v>
-      </c>
-      <c r="AV38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AW38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AX38" s="1"/>
-      <c r="AY38" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK38" s="25"/>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="B39" s="1">
         <v>83</v>
@@ -5187,14 +3348,14 @@
       <c r="R39" s="1">
         <v>0</v>
       </c>
-      <c r="S39" s="39">
+      <c r="S39" s="26">
         <v>4</v>
       </c>
       <c r="T39" s="1">
         <v>28</v>
       </c>
-      <c r="U39" s="35" t="s">
-        <v>37</v>
+      <c r="U39" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -5210,50 +3371,14 @@
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ39" s="1"/>
-      <c r="AK39" s="36"/>
-      <c r="AL39" s="1">
-        <v>6</v>
-      </c>
-      <c r="AM39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="1"/>
-      <c r="AP39" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ39" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="1">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="1">
-        <v>6</v>
-      </c>
-      <c r="AT39" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX39" s="1"/>
-      <c r="AY39" s="1"/>
-    </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK39" s="25"/>
+    </row>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="B40" s="1">
         <v>2</v>
@@ -5304,14 +3429,14 @@
       <c r="R40" s="1">
         <v>91</v>
       </c>
-      <c r="S40" s="45">
-        <v>2</v>
-      </c>
-      <c r="T40" s="45">
-        <v>2</v>
-      </c>
-      <c r="U40" s="35" t="s">
-        <v>37</v>
+      <c r="S40" s="29">
+        <v>2</v>
+      </c>
+      <c r="T40" s="29">
+        <v>2</v>
+      </c>
+      <c r="U40" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="1">
@@ -5348,53 +3473,11 @@
       <c r="AJ40" s="1">
         <v>2</v>
       </c>
-      <c r="AK40" s="36"/>
-      <c r="AL40" s="1">
-        <v>10</v>
-      </c>
-      <c r="AM40" s="1">
-        <v>14</v>
-      </c>
-      <c r="AN40" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AO40" s="1">
-        <v>36</v>
-      </c>
-      <c r="AP40" s="46">
-        <v>1</v>
-      </c>
-      <c r="AQ40" s="37">
-        <v>0.39</v>
-      </c>
-      <c r="AR40" s="1">
-        <v>123</v>
-      </c>
-      <c r="AS40" s="1">
-        <v>75</v>
-      </c>
-      <c r="AT40" s="37">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AU40" s="38">
-        <v>0.01</v>
-      </c>
-      <c r="AV40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX40" s="1">
-        <v>8</v>
-      </c>
-      <c r="AY40" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK40" s="25"/>
+    </row>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -5425,8 +3508,8 @@
       <c r="T41" s="1">
         <v>21</v>
       </c>
-      <c r="U41" s="35" t="s">
-        <v>37</v>
+      <c r="U41" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -5442,52 +3525,16 @@
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ41" s="1">
         <v>1</v>
       </c>
-      <c r="AK41" s="36"/>
-      <c r="AL41" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="1"/>
-      <c r="AP41" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ41" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR41" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS41" s="1">
-        <v>2</v>
-      </c>
-      <c r="AT41" s="37">
-        <v>0</v>
-      </c>
-      <c r="AU41" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX41" s="1"/>
-      <c r="AY41" s="1"/>
-    </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK41" s="25"/>
+    </row>
+    <row r="42" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5518,8 +3565,8 @@
       <c r="T42" s="1">
         <v>27</v>
       </c>
-      <c r="U42" s="35" t="s">
-        <v>37</v>
+      <c r="U42" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -5535,44 +3582,14 @@
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ42" s="1"/>
-      <c r="AK42" s="36"/>
-      <c r="AL42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="37">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="1"/>
-      <c r="AP42" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ42" s="37">
-        <v>0</v>
-      </c>
-      <c r="AR42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="1"/>
-      <c r="AT42" s="1"/>
-      <c r="AU42" s="47"/>
-      <c r="AV42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX42" s="1"/>
-      <c r="AY42" s="1"/>
-    </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AK42" s="25"/>
+    </row>
+    <row r="43" spans="1:37" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" s="1" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
@@ -5619,8 +3636,8 @@
       <c r="T43" s="1">
         <v>11</v>
       </c>
-      <c r="U43" s="35" t="s">
-        <v>37</v>
+      <c r="U43" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -5638,75 +3655,127 @@
         <v>3</v>
       </c>
       <c r="AI43" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="AJ43" s="1">
         <v>3</v>
       </c>
-      <c r="AK43" s="36"/>
-      <c r="AL43" s="1">
+      <c r="AK43" s="25"/>
+    </row>
+    <row r="44" spans="1:37" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B44" s="10">
+        <v>459</v>
+      </c>
+      <c r="C44" s="11">
+        <v>27</v>
+      </c>
+      <c r="D44" s="11">
+        <v>95</v>
+      </c>
+      <c r="E44" s="11">
+        <v>110</v>
+      </c>
+      <c r="F44" s="11">
+        <v>65</v>
+      </c>
+      <c r="G44" s="11">
+        <v>107</v>
+      </c>
+      <c r="H44" s="11">
+        <v>88</v>
+      </c>
+      <c r="I44" s="11">
+        <v>59</v>
+      </c>
+      <c r="J44" s="11">
+        <v>40</v>
+      </c>
+      <c r="K44" s="11">
+        <v>53</v>
+      </c>
+      <c r="L44" s="11">
+        <v>67</v>
+      </c>
+      <c r="M44" s="11">
+        <v>71</v>
+      </c>
+      <c r="N44" s="11">
+        <v>61</v>
+      </c>
+      <c r="O44" s="11">
+        <v>80</v>
+      </c>
+      <c r="P44" s="12">
+        <v>35</v>
+      </c>
+      <c r="Q44" s="12">
+        <v>1417</v>
+      </c>
+      <c r="R44" s="12">
+        <v>661</v>
+      </c>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="13">
+        <v>9</v>
+      </c>
+      <c r="V44" s="14">
+        <v>5</v>
+      </c>
+      <c r="W44" s="14">
+        <v>9</v>
+      </c>
+      <c r="X44" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="14">
         <v>3</v>
       </c>
-      <c r="AM43" s="1">
+      <c r="Z44" s="14">
+        <v>10</v>
+      </c>
+      <c r="AA44" s="14">
+        <v>9</v>
+      </c>
+      <c r="AB44" s="14">
+        <v>6</v>
+      </c>
+      <c r="AC44" s="14">
         <v>3</v>
       </c>
-      <c r="AN43" s="37">
-        <v>0.11</v>
-      </c>
-      <c r="AO43" s="1">
-        <v>21</v>
-      </c>
-      <c r="AP43" s="1">
+      <c r="AD44" s="14">
+        <v>11</v>
+      </c>
+      <c r="AE44" s="14">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="14">
+        <v>10</v>
+      </c>
+      <c r="AG44" s="14">
+        <v>12</v>
+      </c>
+      <c r="AH44" s="14">
+        <v>9</v>
+      </c>
+      <c r="AI44" s="9">
         <v>4</v>
       </c>
-      <c r="AQ43" s="37">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AR43" s="1">
-        <v>46</v>
-      </c>
-      <c r="AS43" s="1">
-        <v>57</v>
-      </c>
-      <c r="AT43" s="37">
-        <v>0.46</v>
-      </c>
-      <c r="AU43" s="38">
-        <v>0</v>
-      </c>
-      <c r="AV43" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW43" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX43" s="1">
-        <v>4</v>
-      </c>
-      <c r="AY43" s="1">
-        <v>13</v>
+      <c r="AJ44" s="15">
+        <f>SUM(AJ4:AJ43)</f>
+        <v>12</v>
+      </c>
+      <c r="AK44" s="16">
+        <f>SUM(AK4:AK43)</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="AT2:AT3"/>
-    <mergeCell ref="AU2:AU3"/>
-    <mergeCell ref="AV2:AV3"/>
-    <mergeCell ref="AW2:AW3"/>
-    <mergeCell ref="AX2:AX3"/>
-    <mergeCell ref="AY2:AY3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="AS2:AS3"/>
+  <mergeCells count="4">
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="U1:AF1"/>
     <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
